--- a/Result/profitability/3441.xlsx
+++ b/Result/profitability/3441.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM72"/>
+  <dimension ref="A1:AM73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.93</v>
       </c>
       <c r="M2" t="n">
-        <v>0.38375</v>
+        <v>0.4475</v>
       </c>
       <c r="N2" t="n">
-        <v>30.56375</v>
+        <v>30.985</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.65</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4424999999999999</v>
+        <v>0.47625</v>
       </c>
       <c r="N3" t="n">
-        <v>28.5925</v>
+        <v>29.2075</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>-0.04</v>
       </c>
       <c r="M4" t="n">
-        <v>0.385</v>
+        <v>0.4225</v>
       </c>
       <c r="N4" t="n">
-        <v>25.3975</v>
+        <v>25.47625</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.11</v>
       </c>
       <c r="M5" t="n">
-        <v>0.35</v>
+        <v>0.51125</v>
       </c>
       <c r="N5" t="n">
-        <v>23.02375</v>
+        <v>24.01625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.55</v>
       </c>
       <c r="M6" t="n">
-        <v>0.49375</v>
+        <v>0.4762500000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>16.52125</v>
+        <v>16.68625</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.17</v>
       </c>
       <c r="M7" t="n">
-        <v>0.41125</v>
+        <v>0.44125</v>
       </c>
       <c r="N7" t="n">
-        <v>15.19125</v>
+        <v>16.72125</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.39</v>
       </c>
       <c r="M8" t="n">
-        <v>0.40375</v>
+        <v>0.43125</v>
       </c>
       <c r="N8" t="n">
-        <v>14.55125</v>
+        <v>15.55625</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9576,6 +9576,133 @@
       </c>
       <c r="AM72" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>3441</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>142</v>
+      </c>
+      <c r="D73" t="n">
+        <v>88</v>
+      </c>
+      <c r="E73" t="n">
+        <v>54</v>
+      </c>
+      <c r="F73" t="n">
+        <v>37.83</v>
+      </c>
+      <c r="G73" t="n">
+        <v>31</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>22.10%</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>6</v>
+      </c>
+      <c r="J73" t="n">
+        <v>37</v>
+      </c>
+      <c r="K73" t="n">
+        <v>28</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="M73" t="n">
+        <v>0.35375</v>
+      </c>
+      <c r="N73" t="n">
+        <v>33.0225</v>
+      </c>
+      <c r="O73" t="n">
+        <v>1</v>
+      </c>
+      <c r="P73" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" t="n">
+        <v>1</v>
+      </c>
+      <c r="S73" t="n">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>0</v>
+      </c>
+      <c r="U73" t="n">
+        <v>0</v>
+      </c>
+      <c r="V73" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W73" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="X73" t="n">
+        <v>0.4680851063829787</v>
+      </c>
+      <c r="Y73" t="n">
+        <v>8.039999999999999</v>
+      </c>
+      <c r="Z73" t="n">
+        <v>0.2698892245720039</v>
+      </c>
+      <c r="AA73" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AB73" t="n">
+        <v>-2.15</v>
+      </c>
+      <c r="AC73" t="n">
+        <v>7.939999999999998</v>
+      </c>
+      <c r="AD73" t="n">
+        <v>0.2656406825025091</v>
+      </c>
+      <c r="AE73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK73" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL73" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM73" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
